--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{4D97D4D6-3DB4-46D0-B8E0-76329EE67857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC31BFAC-89E4-48B4-AFB0-6979E7DDD173}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F66EB-86F1-4876-B9A4-429064D0E2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -386,6 +386,12 @@
   </si>
   <si>
     <t>Rudy Molard</t>
+  </si>
+  <si>
+    <t>Mikel Landa</t>
+  </si>
+  <si>
+    <t>Jan Hirt</t>
   </si>
 </sst>
 </file>
@@ -726,36 +732,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AG21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="32" max="33" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -856,7 +862,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46256</v>
       </c>
@@ -900,7 +906,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46257</v>
       </c>
@@ -944,7 +950,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46258</v>
       </c>
@@ -952,7 +958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46259</v>
       </c>
@@ -1053,7 +1059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46260</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46261</v>
       </c>
@@ -1255,7 +1261,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46262</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46263</v>
       </c>
@@ -1457,7 +1463,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46264</v>
       </c>
@@ -1558,7 +1564,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46266</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46267</v>
       </c>
@@ -1760,7 +1766,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46268</v>
       </c>
@@ -1861,7 +1867,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46269</v>
       </c>
@@ -1962,7 +1968,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46270</v>
       </c>
@@ -2063,7 +2069,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46271</v>
       </c>
@@ -2164,7 +2170,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46273</v>
       </c>
@@ -2265,7 +2271,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46274</v>
       </c>
@@ -2366,7 +2372,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46275</v>
       </c>
@@ -2467,7 +2473,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46276</v>
       </c>
@@ -2565,6 +2571,107 @@
         <v>76</v>
       </c>
       <c r="AG20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" t="s">
+        <v>123</v>
+      </c>
+      <c r="I21" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" t="s">
+        <v>99</v>
+      </c>
+      <c r="N21" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" t="s">
+        <v>57</v>
+      </c>
+      <c r="P21" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>55</v>
+      </c>
+      <c r="R21" t="s">
+        <v>59</v>
+      </c>
+      <c r="S21" t="s">
+        <v>56</v>
+      </c>
+      <c r="T21" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" t="s">
+        <v>76</v>
+      </c>
+      <c r="V21" t="s">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG21" t="s">
         <v>84</v>
       </c>
     </row>

--- a/vuelta-results.xlsx
+++ b/vuelta-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F66EB-86F1-4876-B9A4-429064D0E2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{C99F66EB-86F1-4876-B9A4-429064D0E2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{647C4569-341A-4818-82BA-F8EC17CC712B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>Jan Hirt</t>
+  </si>
+  <si>
+    <t>Pello Bilbao</t>
+  </si>
+  <si>
+    <t>Pau Martí</t>
   </si>
 </sst>
 </file>
@@ -732,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AG22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -2675,6 +2681,107 @@
         <v>84</v>
       </c>
     </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" t="s">
+        <v>125</v>
+      </c>
+      <c r="L22" t="s">
+        <v>103</v>
+      </c>
+      <c r="M22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" t="s">
+        <v>90</v>
+      </c>
+      <c r="O22" t="s">
+        <v>57</v>
+      </c>
+      <c r="P22" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>55</v>
+      </c>
+      <c r="R22" t="s">
+        <v>59</v>
+      </c>
+      <c r="S22" t="s">
+        <v>56</v>
+      </c>
+      <c r="T22" t="s">
+        <v>51</v>
+      </c>
+      <c r="U22" t="s">
+        <v>76</v>
+      </c>
+      <c r="V22" t="s">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
